--- a/resources/tiktok-shop-affiliate/files/ttsa-adv-portfolio-resilience-dashboard.xlsx
+++ b/resources/tiktok-shop-affiliate/files/ttsa-adv-portfolio-resilience-dashboard.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,11 +59,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="5">
     <fill>
@@ -114,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,8 +148,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -580,7 +573,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -758,7 +750,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
@@ -936,7 +927,6 @@
         <v/>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -951,7 +941,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
@@ -962,13 +951,9 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global</t>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="17" t="n"/>
+          <t>ePORTS — your ecom source (eports.global)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1011,7 +996,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
@@ -1068,7 +1052,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
@@ -1150,7 +1133,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
@@ -1251,7 +1233,6 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
@@ -1263,7 +1244,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
@@ -1271,7 +1251,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
@@ -1282,7 +1261,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
